--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.35594583169846</v>
+        <v>5.907841197650999</v>
       </c>
       <c r="D2" t="n">
-        <v>36.36045719955999</v>
+        <v>5.908574294928498</v>
       </c>
       <c r="E2" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F2" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.17718757270181</v>
+        <v>7.178792980564045</v>
       </c>
       <c r="D3" t="n">
-        <v>44.19788280665779</v>
+        <v>7.182155956081891</v>
       </c>
       <c r="E3" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F3" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.99683124953479</v>
+        <v>5.686985078049403</v>
       </c>
       <c r="D4" t="n">
-        <v>35.00661891058905</v>
+        <v>5.688575572970721</v>
       </c>
       <c r="E4" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F4" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.76532989602294</v>
+        <v>2.886866108103727</v>
       </c>
       <c r="D5" t="n">
-        <v>17.77070993234959</v>
+        <v>2.887740364006808</v>
       </c>
       <c r="E5" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F5" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.03542500713964</v>
+        <v>5.205756563660192</v>
       </c>
       <c r="D6" t="n">
-        <v>32.01038727570659</v>
+        <v>5.201687932302321</v>
       </c>
       <c r="E6" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F6" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.50913265910383</v>
+        <v>6.420234057104373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52279520035243</v>
+        <v>6.422454220057269</v>
       </c>
       <c r="E7" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F7" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.44950037406864</v>
+        <v>4.785543810786155</v>
       </c>
       <c r="D8" t="n">
-        <v>29.43771001670463</v>
+        <v>4.783627877714502</v>
       </c>
       <c r="E8" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F8" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.11096854816361</v>
+        <v>7.005532389076587</v>
       </c>
       <c r="D9" t="n">
-        <v>43.1152992890837</v>
+        <v>7.006236134476102</v>
       </c>
       <c r="E9" t="n">
-        <v>7.968416344516779</v>
+        <v>1.294867655983977</v>
       </c>
       <c r="F9" t="n">
-        <v>7.973864611275173</v>
+        <v>1.295752999332216</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
